--- a/workspace/spreadsheets/niches_front_b.xlsx
+++ b/workspace/spreadsheets/niches_front_b.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niches" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phrase Bank" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Niches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phrase Bank" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -916,6 +916,90 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Date Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PHR-0001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ICU Nurse</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Vibes Club</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DSN-B-0001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PHR-0002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ICU Nurse</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Daily Culture</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DSN-B-0002</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
